--- a/data/trans_dic/IP07_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP07_R2-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,42%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,96%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,89%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2,62%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2,52%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,58</t>
+          <t>1,15; 5,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,28</t>
+          <t>0,4; 3,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 6,63</t>
+          <t>0,74; 5,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 6,97</t>
+          <t>1,03; 8,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,96</t>
+          <t>0,94; 5,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,48</t>
+          <t>0,99; 6,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 5,09</t>
+          <t>0,96; 6,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 7,62</t>
+          <t>0,89; 6,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,39</t>
+          <t>1,34; 4,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,97</t>
+          <t>0,88; 3,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,58</t>
+          <t>1,12; 4,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,54</t>
+          <t>1,33; 5,48</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,27%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,29%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,08%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,88</t>
+          <t>3,56; 8,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,28</t>
+          <t>0,59; 3,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,31</t>
+          <t>0,67; 3,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 16,76</t>
+          <t>0,87; 3,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 8,63</t>
+          <t>0,96; 4,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,25</t>
+          <t>0,33; 3,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,93</t>
+          <t>0,86; 4,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,06</t>
+          <t>1,31; 6,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 6,09</t>
+          <t>2,67; 5,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,77</t>
+          <t>0,62; 2,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,35</t>
+          <t>1,08; 3,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 9,16</t>
+          <t>1,41; 4,02</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,73%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,09%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,28</t>
+          <t>0,86; 4,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,77</t>
+          <t>1,86; 6,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,26</t>
+          <t>1,52; 6,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,77</t>
+          <t>0,39; 4,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,19</t>
+          <t>0,45; 3,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 7,02</t>
+          <t>1,43; 5,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,38</t>
+          <t>0,73; 4,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,19</t>
+          <t>1,09; 6,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,72</t>
+          <t>0,91; 3,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,25</t>
+          <t>2,16; 5,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,51</t>
+          <t>1,46; 4,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,56</t>
+          <t>0,96; 4,14</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,42%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>1,28; 5,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,8</t>
+          <t>1,77; 6,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,97</t>
+          <t>0,35; 3,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,62</t>
+          <t>1,76; 6,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,43</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,08</t>
+          <t>1,05; 4,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,45</t>
+          <t>0,28; 2,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,5</t>
+          <t>0,42; 3,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,17</t>
+          <t>0,95; 3,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,48</t>
+          <t>1,86; 4,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,38</t>
+          <t>0,51; 2,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,56</t>
+          <t>1,31; 4,33</t>
         </is>
       </c>
     </row>
@@ -1209,62 +1209,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>1,71%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,34%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,91%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>2,5%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,74</t>
+          <t>2,57; 4,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,42</t>
+          <t>1,67; 3,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,05</t>
+          <t>1,29; 3,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,63</t>
+          <t>1,54; 3,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,7</t>
+          <t>1,01; 2,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,51</t>
+          <t>1,53; 3,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,08</t>
+          <t>1,21; 2,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,62</t>
+          <t>1,58; 3,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,35</t>
+          <t>2,04; 3,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,21</t>
+          <t>1,85; 3,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,66</t>
+          <t>1,49; 2,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,36</t>
+          <t>1,85; 3,3</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3993</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3143</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3819</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3351</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4102</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>3844</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3134</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3993</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3143</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>6990</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1324; 7744</t>
+          <t>1757; 8342</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>955; 8704</t>
+          <t>619; 5375</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1270; 8823</t>
+          <t>1088; 8017</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>968; 8176</t>
+          <t>1300; 10767</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1740; 9076</t>
+          <t>1309; 7457</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>633; 5360</t>
+          <t>1369; 8787</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>662; 7501</t>
+          <t>1281; 9174</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1385; 10697</t>
+          <t>1078; 7923</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3809; 12769</t>
+          <t>3886; 13144</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2911; 11609</t>
+          <t>2586; 11508</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3374; 12839</t>
+          <t>3139; 12390</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3492; 14280</t>
+          <t>3292; 13525</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12140</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4149</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4708</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4432</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2666</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4277</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11210</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12140</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3272</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4149</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16608</t>
+          <t>10759</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1914; 9518</t>
+          <t>7498; 18167</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1211; 6773</t>
+          <t>1304; 7262</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1848; 8884</t>
+          <t>1488; 8632</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4117; 31923</t>
+          <t>2069; 8834</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7402; 18183</t>
+          <t>1883; 8948</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1303; 7221</t>
+          <t>678; 6372</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1580; 8768</t>
+          <t>1772; 8521</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2237; 10361</t>
+          <t>2408; 11284</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11316; 24723</t>
+          <t>10820; 23988</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3215; 11888</t>
+          <t>2673; 10100</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4574; 14378</t>
+          <t>4651; 14199</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8615; 40814</t>
+          <t>5965; 16952</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6320</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5391</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2513</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>2387</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>4773</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3120</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4383</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3312</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6320</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5391</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>7064</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>453; 5904</t>
+          <t>1290; 7348</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2183; 8927</t>
+          <t>3101; 11298</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1125; 6582</t>
+          <t>2527; 10175</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1544; 9086</t>
+          <t>661; 7405</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1289; 7760</t>
+          <t>622; 5465</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3283; 11693</t>
+          <t>2210; 9269</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2577; 10637</t>
+          <t>1136; 7267</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>756; 7766</t>
+          <t>1706; 9652</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2587; 10703</t>
+          <t>2622; 10180</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6608; 16870</t>
+          <t>6925; 16948</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4879; 14480</t>
+          <t>4696; 13922</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3102; 13371</t>
+          <t>3108; 13455</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5969</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2816</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6091</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1474</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5079</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2157</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2417</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5969</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7160</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2816</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8970</t>
+          <t>8459</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5121</t>
+          <t>2647; 10424</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2121; 10061</t>
+          <t>3662; 13294</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>582; 6110</t>
+          <t>711; 7041</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>766; 6073</t>
+          <t>2979; 11332</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2735; 11254</t>
+          <t>0; 5313</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3551; 12585</t>
+          <t>2195; 9711</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>812; 7084</t>
+          <t>582; 5979</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2617; 11789</t>
+          <t>695; 6489</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3984; 13189</t>
+          <t>3947; 12769</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7153; 18673</t>
+          <t>7728; 20306</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2089; 9771</t>
+          <t>2117; 9760</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4511; 15920</t>
+          <t>4419; 14562</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>25414</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>18726</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>15499</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>17131</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>11645</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>16619</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>13398</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>21144</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>25414</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>18726</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>15499</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18669</t>
+          <t>16140</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>39813</t>
+          <t>33271</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7265; 18649</t>
+          <t>18490; 35297</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10563; 24280</t>
+          <t>12486; 26716</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8737; 21336</t>
+          <t>9584; 23187</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12880; 44185</t>
+          <t>10764; 25332</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18030; 33821</t>
+          <t>6868; 18628</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13095; 26308</t>
+          <t>10857; 24748</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9417; 22821</t>
+          <t>8496; 20805</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11965; 27555</t>
+          <t>9944; 24126</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27533; 46954</t>
+          <t>28607; 47605</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26198; 46783</t>
+          <t>27038; 46163</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20921; 38333</t>
+          <t>21541; 37817</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>28069; 62247</t>
+          <t>24678; 43909</t>
         </is>
       </c>
     </row>
